--- a/research/traditional_assets/database/data/bulgaria/bulgaria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_insurance_general.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.17</v>
+        <v>0.419</v>
+      </c>
+      <c r="E2">
+        <v>1.645</v>
       </c>
       <c r="G2">
-        <v>0.001608141702921069</v>
+        <v>0.03848294040123005</v>
       </c>
       <c r="H2">
-        <v>0.001608141702921069</v>
+        <v>0.03848294040123005</v>
       </c>
       <c r="I2">
-        <v>0.01165320074580485</v>
+        <v>0.04844047444721043</v>
       </c>
       <c r="J2">
-        <v>0.01165320074580485</v>
+        <v>0.04391669460214036</v>
       </c>
       <c r="K2">
-        <v>-9.02</v>
+        <v>98.7</v>
       </c>
       <c r="L2">
-        <v>-0.007007458048477314</v>
+        <v>0.02890613559818422</v>
       </c>
       <c r="M2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002157467077612777</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.08536585365853659</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.002157467077612777</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.08536585365853659</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>197.4</v>
+        <v>198.2</v>
       </c>
       <c r="V2">
-        <v>0.5530961053516391</v>
+        <v>0.7739164388910581</v>
       </c>
       <c r="W2">
-        <v>-0.1005574136008918</v>
+        <v>0.6610850636302746</v>
       </c>
       <c r="X2">
-        <v>0.1284241414834437</v>
+        <v>0.2231559282312581</v>
       </c>
       <c r="Y2">
-        <v>-0.2289815550843355</v>
+        <v>0.4379291353990165</v>
       </c>
       <c r="Z2">
-        <v>10.45653939886271</v>
+        <v>6.598067632850242</v>
       </c>
       <c r="AA2">
-        <v>0.1218521527213647</v>
+        <v>0.2897653211961512</v>
       </c>
       <c r="AB2">
-        <v>0.06741325300312966</v>
+        <v>0.1087369869088308</v>
       </c>
       <c r="AC2">
-        <v>0.05443889971823508</v>
+        <v>0.1810283342873204</v>
       </c>
       <c r="AD2">
-        <v>725.4</v>
+        <v>703.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>725.4</v>
+        <v>703.8</v>
       </c>
       <c r="AG2">
-        <v>528</v>
+        <v>505.6</v>
       </c>
       <c r="AH2">
-        <v>0.6702393051834057</v>
+        <v>0.733201375143244</v>
       </c>
       <c r="AI2">
-        <v>0.6901998097050428</v>
+        <v>0.7916760404949381</v>
       </c>
       <c r="AJ2">
-        <v>0.5966775906882134</v>
+        <v>0.6637783904424314</v>
       </c>
       <c r="AK2">
-        <v>0.6185567010309279</v>
+        <v>0.7319050376375217</v>
       </c>
       <c r="AL2">
-        <v>19.8</v>
+        <v>42.3</v>
       </c>
       <c r="AM2">
-        <v>19.161</v>
+        <v>41.708</v>
       </c>
       <c r="AN2">
-        <v>26.57142857142857</v>
+        <v>3.197637437528396</v>
       </c>
       <c r="AO2">
-        <v>0.7575757575757576</v>
+        <v>3.91016548463357</v>
       </c>
       <c r="AP2">
-        <v>19.34065934065934</v>
+        <v>2.297137664697865</v>
       </c>
       <c r="AQ2">
-        <v>0.7828401440425864</v>
+        <v>3.965666059269205</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.17</v>
+        <v>0.419</v>
+      </c>
+      <c r="E3">
+        <v>1.645</v>
       </c>
       <c r="G3">
-        <v>0.001608141702921069</v>
+        <v>0.03848294040123005</v>
       </c>
       <c r="H3">
-        <v>0.001608141702921069</v>
+        <v>0.03848294040123005</v>
       </c>
       <c r="I3">
-        <v>0.01165320074580485</v>
+        <v>0.04844047444721043</v>
       </c>
       <c r="J3">
-        <v>0.01165320074580485</v>
+        <v>0.04391669460214036</v>
       </c>
       <c r="K3">
-        <v>-9.02</v>
+        <v>98.7</v>
       </c>
       <c r="L3">
-        <v>-0.007007458048477314</v>
+        <v>0.02890613559818422</v>
       </c>
       <c r="M3">
-        <v>0.77</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.002157467077612777</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.08536585365853659</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.77</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.002157467077612777</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.08536585365853659</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>197.4</v>
+        <v>198.2</v>
       </c>
       <c r="V3">
-        <v>0.5530961053516391</v>
+        <v>0.7739164388910581</v>
       </c>
       <c r="W3">
-        <v>-0.1005574136008918</v>
+        <v>0.6610850636302746</v>
       </c>
       <c r="X3">
-        <v>0.1284241414834437</v>
+        <v>0.2231559282312581</v>
       </c>
       <c r="Y3">
-        <v>-0.2289815550843355</v>
+        <v>0.4379291353990165</v>
       </c>
       <c r="Z3">
-        <v>10.45653939886271</v>
+        <v>6.598067632850242</v>
       </c>
       <c r="AA3">
-        <v>0.1218521527213647</v>
+        <v>0.2897653211961512</v>
       </c>
       <c r="AB3">
-        <v>0.06741325300312966</v>
+        <v>0.1087369869088308</v>
       </c>
       <c r="AC3">
-        <v>0.05443889971823508</v>
+        <v>0.1810283342873204</v>
       </c>
       <c r="AD3">
-        <v>725.4</v>
+        <v>703.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>725.4</v>
+        <v>703.8</v>
       </c>
       <c r="AG3">
-        <v>528</v>
+        <v>505.6</v>
       </c>
       <c r="AH3">
-        <v>0.6702393051834057</v>
+        <v>0.733201375143244</v>
       </c>
       <c r="AI3">
-        <v>0.6901998097050428</v>
+        <v>0.7916760404949381</v>
       </c>
       <c r="AJ3">
-        <v>0.5966775906882134</v>
+        <v>0.6637783904424314</v>
       </c>
       <c r="AK3">
-        <v>0.6185567010309279</v>
+        <v>0.7319050376375217</v>
       </c>
       <c r="AL3">
-        <v>19.8</v>
+        <v>42.3</v>
       </c>
       <c r="AM3">
-        <v>19.161</v>
+        <v>41.708</v>
       </c>
       <c r="AN3">
-        <v>26.57142857142857</v>
+        <v>3.197637437528396</v>
       </c>
       <c r="AO3">
-        <v>0.7575757575757576</v>
+        <v>3.91016548463357</v>
       </c>
       <c r="AP3">
-        <v>19.34065934065934</v>
+        <v>2.297137664697865</v>
       </c>
       <c r="AQ3">
-        <v>0.7828401440425864</v>
+        <v>3.965666059269205</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_insurance_general.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.419</v>
-      </c>
-      <c r="E2">
-        <v>1.645</v>
+        <v>0.256</v>
       </c>
       <c r="G2">
-        <v>0.03848294040123005</v>
+        <v>0.06474232745785506</v>
       </c>
       <c r="H2">
-        <v>0.03848294040123005</v>
+        <v>0.06474232745785506</v>
       </c>
       <c r="I2">
-        <v>0.04844047444721043</v>
+        <v>0.09207050573939772</v>
       </c>
       <c r="J2">
-        <v>0.04391669460214036</v>
+        <v>0.08310719433522065</v>
       </c>
       <c r="K2">
-        <v>98.7</v>
+        <v>-36.7</v>
       </c>
       <c r="L2">
-        <v>0.02890613559818422</v>
+        <v>-0.01762643484943087</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>198.2</v>
+        <v>120.2</v>
       </c>
       <c r="V2">
-        <v>0.7739164388910581</v>
+        <v>0.4811849479583667</v>
       </c>
       <c r="W2">
-        <v>0.6610850636302746</v>
+        <v>-0.2282338308457711</v>
       </c>
       <c r="X2">
-        <v>0.2231559282312581</v>
+        <v>0.1945102570362252</v>
       </c>
       <c r="Y2">
-        <v>0.4379291353990165</v>
+        <v>-0.4227440878819964</v>
       </c>
       <c r="Z2">
-        <v>6.598067632850242</v>
+        <v>3.580567497850387</v>
       </c>
       <c r="AA2">
-        <v>0.2897653211961512</v>
+        <v>0.2975709188742269</v>
       </c>
       <c r="AB2">
-        <v>0.1087369869088308</v>
+        <v>0.09171708482770702</v>
       </c>
       <c r="AC2">
-        <v>0.1810283342873204</v>
+        <v>0.2058538340465199</v>
       </c>
       <c r="AD2">
-        <v>703.8</v>
+        <v>723.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>703.8</v>
+        <v>723.2</v>
       </c>
       <c r="AG2">
-        <v>505.6</v>
+        <v>603</v>
       </c>
       <c r="AH2">
-        <v>0.733201375143244</v>
+        <v>0.7432682425488182</v>
       </c>
       <c r="AI2">
-        <v>0.7916760404949381</v>
+        <v>0.8338521849417733</v>
       </c>
       <c r="AJ2">
-        <v>0.6637783904424314</v>
+        <v>0.7070825515947468</v>
       </c>
       <c r="AK2">
-        <v>0.7319050376375217</v>
+        <v>0.8071208673537679</v>
       </c>
       <c r="AL2">
-        <v>42.3</v>
+        <v>60.7</v>
       </c>
       <c r="AM2">
-        <v>41.708</v>
+        <v>58.78</v>
       </c>
       <c r="AN2">
-        <v>3.197637437528396</v>
+        <v>2.944625407166124</v>
       </c>
       <c r="AO2">
-        <v>3.91016548463357</v>
+        <v>3.158154859967051</v>
       </c>
       <c r="AP2">
-        <v>2.297137664697865</v>
+        <v>2.455211726384365</v>
       </c>
       <c r="AQ2">
-        <v>3.965666059269205</v>
+        <v>3.261313371895202</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.419</v>
-      </c>
-      <c r="E3">
-        <v>1.645</v>
+        <v>0.256</v>
       </c>
       <c r="G3">
-        <v>0.03848294040123005</v>
+        <v>0.06474232745785506</v>
       </c>
       <c r="H3">
-        <v>0.03848294040123005</v>
+        <v>0.06474232745785506</v>
       </c>
       <c r="I3">
-        <v>0.04844047444721043</v>
+        <v>0.09207050573939772</v>
       </c>
       <c r="J3">
-        <v>0.04391669460214036</v>
+        <v>0.08310719433522065</v>
       </c>
       <c r="K3">
-        <v>98.7</v>
+        <v>-36.7</v>
       </c>
       <c r="L3">
-        <v>0.02890613559818422</v>
+        <v>-0.01762643484943087</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>198.2</v>
+        <v>120.2</v>
       </c>
       <c r="V3">
-        <v>0.7739164388910581</v>
+        <v>0.4811849479583667</v>
       </c>
       <c r="W3">
-        <v>0.6610850636302746</v>
+        <v>-0.2282338308457711</v>
       </c>
       <c r="X3">
-        <v>0.2231559282312581</v>
+        <v>0.1945102570362252</v>
       </c>
       <c r="Y3">
-        <v>0.4379291353990165</v>
+        <v>-0.4227440878819964</v>
       </c>
       <c r="Z3">
-        <v>6.598067632850242</v>
+        <v>3.580567497850387</v>
       </c>
       <c r="AA3">
-        <v>0.2897653211961512</v>
+        <v>0.2975709188742269</v>
       </c>
       <c r="AB3">
-        <v>0.1087369869088308</v>
+        <v>0.09171708482770702</v>
       </c>
       <c r="AC3">
-        <v>0.1810283342873204</v>
+        <v>0.2058538340465199</v>
       </c>
       <c r="AD3">
-        <v>703.8</v>
+        <v>723.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>703.8</v>
+        <v>723.2</v>
       </c>
       <c r="AG3">
-        <v>505.6</v>
+        <v>603</v>
       </c>
       <c r="AH3">
-        <v>0.733201375143244</v>
+        <v>0.7432682425488182</v>
       </c>
       <c r="AI3">
-        <v>0.7916760404949381</v>
+        <v>0.8338521849417733</v>
       </c>
       <c r="AJ3">
-        <v>0.6637783904424314</v>
+        <v>0.7070825515947468</v>
       </c>
       <c r="AK3">
-        <v>0.7319050376375217</v>
+        <v>0.8071208673537679</v>
       </c>
       <c r="AL3">
-        <v>42.3</v>
+        <v>60.7</v>
       </c>
       <c r="AM3">
-        <v>41.708</v>
+        <v>58.78</v>
       </c>
       <c r="AN3">
-        <v>3.197637437528396</v>
+        <v>2.944625407166124</v>
       </c>
       <c r="AO3">
-        <v>3.91016548463357</v>
+        <v>3.158154859967051</v>
       </c>
       <c r="AP3">
-        <v>2.297137664697865</v>
+        <v>2.455211726384365</v>
       </c>
       <c r="AQ3">
-        <v>3.965666059269205</v>
+        <v>3.261313371895202</v>
       </c>
     </row>
   </sheetData>
